--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ60"/>
+  <dimension ref="A1:AZ69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135530557</v>
+        <v>136735432</v>
       </c>
       <c r="B2" t="n">
-        <v>79460</v>
+        <v>93398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745289</v>
+        <v>745633</v>
       </c>
       <c r="R2" t="n">
-        <v>7201361</v>
+        <v>7201149</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +775,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530557</t>
+          <t>https://artportalen.se/Sighting/136735432</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135530558</v>
+        <v>136735435</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>93408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745276</v>
+        <v>745575</v>
       </c>
       <c r="R3" t="n">
-        <v>7201299</v>
+        <v>7201201</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,69 +891,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530558</t>
+          <t>https://artportalen.se/Sighting/136735435</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135530559</v>
+        <v>136735430</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>93048</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745236</v>
+        <v>745678</v>
       </c>
       <c r="R4" t="n">
-        <v>7201208</v>
+        <v>7201079</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,31 +1007,31 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530559</t>
+          <t>https://artportalen.se/Sighting/136735430</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135530567</v>
+        <v>136735426</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>90891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,37 +1039,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745105</v>
+        <v>745736</v>
       </c>
       <c r="R5" t="n">
-        <v>7201186</v>
+        <v>7200987</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,22 +1093,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,31 +1123,31 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530567</t>
+          <t>https://artportalen.se/Sighting/136735426</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135530570</v>
+        <v>136735427</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>90891</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,37 +1155,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745072</v>
+        <v>745701</v>
       </c>
       <c r="R6" t="n">
-        <v>7201155</v>
+        <v>7200979</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,22 +1209,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,31 +1239,31 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530570</t>
+          <t>https://artportalen.se/Sighting/136735427</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135530571</v>
+        <v>136735433</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>90891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,37 +1271,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745071</v>
+        <v>745611</v>
       </c>
       <c r="R7" t="n">
-        <v>7201129</v>
+        <v>7201151</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1325,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,28 +1355,28 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530571</t>
+          <t>https://artportalen.se/Sighting/136735433</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135530572</v>
+        <v>135530557</v>
       </c>
       <c r="B8" t="n">
         <v>79460</v>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745062</v>
+        <v>745289</v>
       </c>
       <c r="R8" t="n">
-        <v>7201112</v>
+        <v>7201361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,13 +1486,13 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530572</t>
+          <t>https://artportalen.se/Sighting/135530557</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135530574</v>
+        <v>135530558</v>
       </c>
       <c r="B9" t="n">
         <v>79460</v>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745036</v>
+        <v>745276</v>
       </c>
       <c r="R9" t="n">
-        <v>7201097</v>
+        <v>7201299</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,13 +1602,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530574</t>
+          <t>https://artportalen.se/Sighting/135530558</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135530576</v>
+        <v>135530559</v>
       </c>
       <c r="B10" t="n">
         <v>79460</v>
@@ -1643,10 +1643,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745030</v>
+        <v>745236</v>
       </c>
       <c r="R10" t="n">
-        <v>7201106</v>
+        <v>7201208</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,13 +1718,13 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530576</t>
+          <t>https://artportalen.se/Sighting/135530559</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135530577</v>
+        <v>135530567</v>
       </c>
       <c r="B11" t="n">
         <v>79460</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>744996</v>
+        <v>745105</v>
       </c>
       <c r="R11" t="n">
-        <v>7201075</v>
+        <v>7201186</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,13 +1834,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530577</t>
+          <t>https://artportalen.se/Sighting/135530567</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135530579</v>
+        <v>135530570</v>
       </c>
       <c r="B12" t="n">
         <v>79460</v>
@@ -1875,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745068</v>
+        <v>745072</v>
       </c>
       <c r="R12" t="n">
-        <v>7201004</v>
+        <v>7201155</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,13 +1950,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530579</t>
+          <t>https://artportalen.se/Sighting/135530570</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135530580</v>
+        <v>135530571</v>
       </c>
       <c r="B13" t="n">
         <v>79460</v>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745103</v>
+        <v>745071</v>
       </c>
       <c r="R13" t="n">
-        <v>7201015</v>
+        <v>7201129</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,13 +2066,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530580</t>
+          <t>https://artportalen.se/Sighting/135530571</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135530582</v>
+        <v>135530572</v>
       </c>
       <c r="B14" t="n">
         <v>79460</v>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745109</v>
+        <v>745062</v>
       </c>
       <c r="R14" t="n">
-        <v>7200985</v>
+        <v>7201112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,12 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Flera träd</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,13 +2182,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530582</t>
+          <t>https://artportalen.se/Sighting/135530572</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135530583</v>
+        <v>135530574</v>
       </c>
       <c r="B15" t="n">
         <v>79460</v>
@@ -2228,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745138</v>
+        <v>745036</v>
       </c>
       <c r="R15" t="n">
-        <v>7200924</v>
+        <v>7201097</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,13 +2298,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530583</t>
+          <t>https://artportalen.se/Sighting/135530574</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135530584</v>
+        <v>135530576</v>
       </c>
       <c r="B16" t="n">
         <v>79460</v>
@@ -2344,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745188</v>
+        <v>745030</v>
       </c>
       <c r="R16" t="n">
-        <v>7200877</v>
+        <v>7201106</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,13 +2414,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530584</t>
+          <t>https://artportalen.se/Sighting/135530576</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135530585</v>
+        <v>135530577</v>
       </c>
       <c r="B17" t="n">
         <v>79460</v>
@@ -2460,10 +2455,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745178</v>
+        <v>744996</v>
       </c>
       <c r="R17" t="n">
-        <v>7200888</v>
+        <v>7201075</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,12 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2540,13 +2530,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530585</t>
+          <t>https://artportalen.se/Sighting/135530577</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135530586</v>
+        <v>135530579</v>
       </c>
       <c r="B18" t="n">
         <v>79460</v>
@@ -2581,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745241</v>
+        <v>745068</v>
       </c>
       <c r="R18" t="n">
-        <v>7200789</v>
+        <v>7201004</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2616,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2656,13 +2646,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530586</t>
+          <t>https://artportalen.se/Sighting/135530579</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135530587</v>
+        <v>135530580</v>
       </c>
       <c r="B19" t="n">
         <v>79460</v>
@@ -2697,10 +2687,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745339</v>
+        <v>745103</v>
       </c>
       <c r="R19" t="n">
-        <v>7200794</v>
+        <v>7201015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2732,7 +2722,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2742,7 +2732,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,13 +2762,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530587</t>
+          <t>https://artportalen.se/Sighting/135530580</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135530592</v>
+        <v>135530582</v>
       </c>
       <c r="B20" t="n">
         <v>79460</v>
@@ -2813,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745345</v>
+        <v>745109</v>
       </c>
       <c r="R20" t="n">
-        <v>7200823</v>
+        <v>7200985</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2848,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2858,7 +2848,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2888,13 +2883,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530592</t>
+          <t>https://artportalen.se/Sighting/135530582</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135530594</v>
+        <v>135530583</v>
       </c>
       <c r="B21" t="n">
         <v>79460</v>
@@ -2929,10 +2924,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745322</v>
+        <v>745138</v>
       </c>
       <c r="R21" t="n">
-        <v>7200832</v>
+        <v>7200924</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,7 +2959,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2974,7 +2969,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3004,13 +2999,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530594</t>
+          <t>https://artportalen.se/Sighting/135530583</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135530596</v>
+        <v>135530584</v>
       </c>
       <c r="B22" t="n">
         <v>79460</v>
@@ -3039,19 +3034,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745314</v>
+        <v>745188</v>
       </c>
       <c r="R22" t="n">
-        <v>7200859</v>
+        <v>7200877</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3083,7 +3075,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3093,7 +3085,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3102,7 +3094,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3124,13 +3115,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530596</t>
+          <t>https://artportalen.se/Sighting/135530584</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135530603</v>
+        <v>135530585</v>
       </c>
       <c r="B23" t="n">
         <v>79460</v>
@@ -3165,10 +3156,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745329</v>
+        <v>745178</v>
       </c>
       <c r="R23" t="n">
-        <v>7200907</v>
+        <v>7200888</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3200,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3210,7 +3201,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3245,13 +3236,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530603</t>
+          <t>https://artportalen.se/Sighting/135530585</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135530604</v>
+        <v>135530586</v>
       </c>
       <c r="B24" t="n">
         <v>79460</v>
@@ -3286,10 +3277,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745301</v>
+        <v>745241</v>
       </c>
       <c r="R24" t="n">
-        <v>7200917</v>
+        <v>7200789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3321,7 +3312,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3331,12 +3322,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bilder</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3366,13 +3352,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530604</t>
+          <t>https://artportalen.se/Sighting/135530586</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135530606</v>
+        <v>135530587</v>
       </c>
       <c r="B25" t="n">
         <v>79460</v>
@@ -3407,10 +3393,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745315</v>
+        <v>745339</v>
       </c>
       <c r="R25" t="n">
-        <v>7200949</v>
+        <v>7200794</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3442,7 +3428,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3452,7 +3438,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,13 +3468,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530606</t>
+          <t>https://artportalen.se/Sighting/135530587</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135530607</v>
+        <v>135530592</v>
       </c>
       <c r="B26" t="n">
         <v>79460</v>
@@ -3523,10 +3509,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745287</v>
+        <v>745345</v>
       </c>
       <c r="R26" t="n">
-        <v>7200957</v>
+        <v>7200823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3558,7 +3544,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3568,12 +3554,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3603,13 +3584,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530607</t>
+          <t>https://artportalen.se/Sighting/135530592</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135530611</v>
+        <v>135530594</v>
       </c>
       <c r="B27" t="n">
         <v>79460</v>
@@ -3644,10 +3625,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745294</v>
+        <v>745322</v>
       </c>
       <c r="R27" t="n">
-        <v>7201009</v>
+        <v>7200832</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3679,7 +3660,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3689,7 +3670,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3719,13 +3700,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530611</t>
+          <t>https://artportalen.se/Sighting/135530594</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135530616</v>
+        <v>135530596</v>
       </c>
       <c r="B28" t="n">
         <v>79460</v>
@@ -3754,16 +3735,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745272</v>
+        <v>745314</v>
       </c>
       <c r="R28" t="n">
-        <v>7201118</v>
+        <v>7200859</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3795,7 +3779,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3805,7 +3789,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3814,6 +3798,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3835,13 +3820,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530616</t>
+          <t>https://artportalen.se/Sighting/135530596</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135530617</v>
+        <v>135530603</v>
       </c>
       <c r="B29" t="n">
         <v>79460</v>
@@ -3876,10 +3861,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745239</v>
+        <v>745329</v>
       </c>
       <c r="R29" t="n">
-        <v>7201178</v>
+        <v>7200907</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3911,7 +3896,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3921,7 +3906,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3951,13 +3941,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530617</t>
+          <t>https://artportalen.se/Sighting/135530603</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135530618</v>
+        <v>135530604</v>
       </c>
       <c r="B30" t="n">
         <v>79460</v>
@@ -3992,10 +3982,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745225</v>
+        <v>745301</v>
       </c>
       <c r="R30" t="n">
-        <v>7201291</v>
+        <v>7200917</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4027,7 +4017,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4037,7 +4027,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4067,13 +4062,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530618</t>
+          <t>https://artportalen.se/Sighting/135530604</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135530626</v>
+        <v>135530606</v>
       </c>
       <c r="B31" t="n">
         <v>79460</v>
@@ -4108,10 +4103,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745686</v>
+        <v>745315</v>
       </c>
       <c r="R31" t="n">
-        <v>7200954</v>
+        <v>7200949</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4143,7 +4138,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4153,7 +4148,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4183,38 +4178,38 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530626</t>
+          <t>https://artportalen.se/Sighting/135530606</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135530578</v>
+        <v>135530607</v>
       </c>
       <c r="B32" t="n">
-        <v>78863</v>
+        <v>79460</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4224,10 +4219,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745042</v>
+        <v>745287</v>
       </c>
       <c r="R32" t="n">
-        <v>7201067</v>
+        <v>7200957</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4259,7 +4254,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4269,7 +4264,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4299,38 +4299,38 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530578</t>
+          <t>https://artportalen.se/Sighting/135530607</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135530560</v>
+        <v>135530611</v>
       </c>
       <c r="B33" t="n">
-        <v>79217</v>
+        <v>79460</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745246</v>
+        <v>745294</v>
       </c>
       <c r="R33" t="n">
-        <v>7201169</v>
+        <v>7201009</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4375,7 +4375,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4415,38 +4415,38 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530560</t>
+          <t>https://artportalen.se/Sighting/135530611</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135530598</v>
+        <v>135530616</v>
       </c>
       <c r="B34" t="n">
-        <v>80575</v>
+        <v>79460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4456,10 +4456,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745329</v>
+        <v>745272</v>
       </c>
       <c r="R34" t="n">
-        <v>7200885</v>
+        <v>7201118</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4491,7 +4491,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4531,38 +4531,38 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530598</t>
+          <t>https://artportalen.se/Sighting/135530616</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135530608</v>
+        <v>135530617</v>
       </c>
       <c r="B35" t="n">
-        <v>80575</v>
+        <v>79460</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4572,10 +4572,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745270</v>
+        <v>745239</v>
       </c>
       <c r="R35" t="n">
-        <v>7200986</v>
+        <v>7201178</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4647,38 +4647,38 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530608</t>
+          <t>https://artportalen.se/Sighting/135530617</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135530613</v>
+        <v>135530618</v>
       </c>
       <c r="B36" t="n">
-        <v>80575</v>
+        <v>79460</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4688,10 +4688,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745318</v>
+        <v>745225</v>
       </c>
       <c r="R36" t="n">
-        <v>7201025</v>
+        <v>7201291</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4733,12 +4733,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4768,38 +4763,38 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530613</t>
+          <t>https://artportalen.se/Sighting/135530618</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135530599</v>
+        <v>135530626</v>
       </c>
       <c r="B37" t="n">
-        <v>80580</v>
+        <v>79460</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4809,10 +4804,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745333</v>
+        <v>745686</v>
       </c>
       <c r="R37" t="n">
-        <v>7200883</v>
+        <v>7200954</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4844,7 +4839,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4854,7 +4849,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4884,38 +4879,38 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530599</t>
+          <t>https://artportalen.se/Sighting/135530626</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135530600</v>
+        <v>135530578</v>
       </c>
       <c r="B38" t="n">
-        <v>80586</v>
+        <v>78863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6463</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4925,10 +4920,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745333</v>
+        <v>745042</v>
       </c>
       <c r="R38" t="n">
-        <v>7200883</v>
+        <v>7201067</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4960,7 +4955,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4970,7 +4965,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5000,38 +4995,38 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530600</t>
+          <t>https://artportalen.se/Sighting/135530578</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135530609</v>
+        <v>135530560</v>
       </c>
       <c r="B39" t="n">
-        <v>80586</v>
+        <v>79217</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5041,10 +5036,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745276</v>
+        <v>745246</v>
       </c>
       <c r="R39" t="n">
-        <v>7200976</v>
+        <v>7201169</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5076,7 +5071,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5086,7 +5081,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5116,16 +5111,16 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530609</t>
+          <t>https://artportalen.se/Sighting/135530560</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135530562</v>
+        <v>135530598</v>
       </c>
       <c r="B40" t="n">
-        <v>57993</v>
+        <v>80575</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5133,39 +5128,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745221</v>
+        <v>745329</v>
       </c>
       <c r="R40" t="n">
-        <v>7201177</v>
+        <v>7200885</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5197,7 +5187,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5207,12 +5197,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bikder</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5242,16 +5227,16 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530562</t>
+          <t>https://artportalen.se/Sighting/135530598</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135530563</v>
+        <v>135530608</v>
       </c>
       <c r="B41" t="n">
-        <v>57993</v>
+        <v>80575</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5259,39 +5244,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745147</v>
+        <v>745270</v>
       </c>
       <c r="R41" t="n">
-        <v>7201197</v>
+        <v>7200986</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5323,7 +5303,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5333,12 +5313,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bilder</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5368,16 +5343,16 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530563</t>
+          <t>https://artportalen.se/Sighting/135530608</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135530564</v>
+        <v>135530613</v>
       </c>
       <c r="B42" t="n">
-        <v>57993</v>
+        <v>80575</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5385,39 +5360,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745132</v>
+        <v>745318</v>
       </c>
       <c r="R42" t="n">
-        <v>7201209</v>
+        <v>7201025</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5449,7 +5419,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5459,12 +5429,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5494,56 +5464,51 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530564</t>
+          <t>https://artportalen.se/Sighting/135530613</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135530565</v>
+        <v>135530599</v>
       </c>
       <c r="B43" t="n">
-        <v>57993</v>
+        <v>80580</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745109</v>
+        <v>745333</v>
       </c>
       <c r="R43" t="n">
-        <v>7201209</v>
+        <v>7200883</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5575,7 +5540,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5585,12 +5550,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5620,56 +5580,51 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530565</t>
+          <t>https://artportalen.se/Sighting/135530599</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135530566</v>
+        <v>135530600</v>
       </c>
       <c r="B44" t="n">
-        <v>57993</v>
+        <v>80586</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745100</v>
+        <v>745333</v>
       </c>
       <c r="R44" t="n">
-        <v>7201200</v>
+        <v>7200883</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5701,7 +5656,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5711,12 +5666,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:57</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5746,56 +5696,51 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530566</t>
+          <t>https://artportalen.se/Sighting/135530600</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135530573</v>
+        <v>135530609</v>
       </c>
       <c r="B45" t="n">
-        <v>57993</v>
+        <v>80586</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745046</v>
+        <v>745276</v>
       </c>
       <c r="R45" t="n">
-        <v>7201117</v>
+        <v>7200976</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5827,7 +5772,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5837,12 +5782,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:04</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack bilder</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5872,13 +5812,13 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530573</t>
+          <t>https://artportalen.se/Sighting/135530609</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135530588</v>
+        <v>135530562</v>
       </c>
       <c r="B46" t="n">
         <v>57993</v>
@@ -5907,24 +5847,21 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745362</v>
+        <v>745221</v>
       </c>
       <c r="R46" t="n">
-        <v>7200804</v>
+        <v>7201177</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5956,7 +5893,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5966,12 +5903,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack bikder</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6001,13 +5938,13 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530588</t>
+          <t>https://artportalen.se/Sighting/135530562</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135530590</v>
+        <v>135530563</v>
       </c>
       <c r="B47" t="n">
         <v>57993</v>
@@ -6047,10 +5984,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745376</v>
+        <v>745147</v>
       </c>
       <c r="R47" t="n">
-        <v>7200807</v>
+        <v>7201197</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6082,7 +6019,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6092,12 +6029,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack bild</t>
+          <t>Äldre ringhack bilder</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6127,13 +6064,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530590</t>
+          <t>https://artportalen.se/Sighting/135530563</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135530605</v>
+        <v>135530564</v>
       </c>
       <c r="B48" t="n">
         <v>57993</v>
@@ -6162,24 +6099,21 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745287</v>
+        <v>745132</v>
       </c>
       <c r="R48" t="n">
-        <v>7200930</v>
+        <v>7201209</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6211,7 +6145,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6221,19 +6155,19 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Skalad gran</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="b">
         <v>0</v>
@@ -6256,13 +6190,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530605</t>
+          <t>https://artportalen.se/Sighting/135530564</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135530610</v>
+        <v>135530565</v>
       </c>
       <c r="B49" t="n">
         <v>57993</v>
@@ -6291,24 +6225,21 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745278</v>
+        <v>745109</v>
       </c>
       <c r="R49" t="n">
-        <v>7201005</v>
+        <v>7201209</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6340,7 +6271,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6350,12 +6281,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska (?) ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6385,13 +6316,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530610</t>
+          <t>https://artportalen.se/Sighting/135530565</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135530612</v>
+        <v>135530566</v>
       </c>
       <c r="B50" t="n">
         <v>57993</v>
@@ -6422,7 +6353,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6431,10 +6362,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745307</v>
+        <v>745100</v>
       </c>
       <c r="R50" t="n">
-        <v>7201037</v>
+        <v>7201200</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6466,7 +6397,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6476,12 +6407,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6511,13 +6442,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530612</t>
+          <t>https://artportalen.se/Sighting/135530566</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135530614</v>
+        <v>135530573</v>
       </c>
       <c r="B51" t="n">
         <v>57993</v>
@@ -6557,10 +6488,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>745306</v>
+        <v>745046</v>
       </c>
       <c r="R51" t="n">
-        <v>7201046</v>
+        <v>7201117</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6592,7 +6523,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6602,12 +6533,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack bild</t>
+          <t>Färska ringhack bilder</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6637,13 +6568,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530614</t>
+          <t>https://artportalen.se/Sighting/135530573</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135530615</v>
+        <v>135530588</v>
       </c>
       <c r="B52" t="n">
         <v>57993</v>
@@ -6672,21 +6603,24 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>745282</v>
+        <v>745362</v>
       </c>
       <c r="R52" t="n">
-        <v>7201100</v>
+        <v>7200804</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6718,7 +6652,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6728,12 +6662,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack bild</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6763,13 +6697,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530615</t>
+          <t>https://artportalen.se/Sighting/135530588</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135530619</v>
+        <v>135530590</v>
       </c>
       <c r="B53" t="n">
         <v>57993</v>
@@ -6809,10 +6743,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>745225</v>
+        <v>745376</v>
       </c>
       <c r="R53" t="n">
-        <v>7201291</v>
+        <v>7200807</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6844,7 +6778,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6854,12 +6788,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6889,16 +6823,16 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530619</t>
+          <t>https://artportalen.se/Sighting/135530590</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135530575</v>
+        <v>135530605</v>
       </c>
       <c r="B54" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6906,39 +6840,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>745036</v>
+        <v>745287</v>
       </c>
       <c r="R54" t="n">
-        <v>7201097</v>
+        <v>7200930</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6970,7 +6907,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6980,19 +6917,19 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -7015,16 +6952,16 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530575</t>
+          <t>https://artportalen.se/Sighting/135530605</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135530581</v>
+        <v>135530610</v>
       </c>
       <c r="B55" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7032,39 +6969,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>745092</v>
+        <v>745278</v>
       </c>
       <c r="R55" t="n">
-        <v>7200970</v>
+        <v>7201005</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7096,7 +7036,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7106,12 +7046,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Färska (?) ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7141,16 +7081,16 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530581</t>
+          <t>https://artportalen.se/Sighting/135530610</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135530593</v>
+        <v>135530612</v>
       </c>
       <c r="B56" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7158,27 +7098,27 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7187,10 +7127,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>745345</v>
+        <v>745307</v>
       </c>
       <c r="R56" t="n">
-        <v>7200823</v>
+        <v>7201037</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7222,7 +7162,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7232,12 +7172,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Läten flera st</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7267,16 +7207,16 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530593</t>
+          <t>https://artportalen.se/Sighting/135530612</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135530595</v>
+        <v>135530614</v>
       </c>
       <c r="B57" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7284,27 +7224,27 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7313,10 +7253,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>745322</v>
+        <v>745306</v>
       </c>
       <c r="R57" t="n">
-        <v>7200832</v>
+        <v>7201046</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7348,7 +7288,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7358,12 +7298,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Läten</t>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7393,51 +7333,56 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530595</t>
+          <t>https://artportalen.se/Sighting/135530614</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135530624</v>
+        <v>135530615</v>
       </c>
       <c r="B58" t="n">
-        <v>98196</v>
+        <v>57993</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>745746</v>
+        <v>745282</v>
       </c>
       <c r="R58" t="n">
-        <v>7200976</v>
+        <v>7201100</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7469,7 +7414,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7479,7 +7424,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7509,51 +7459,56 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530624</t>
+          <t>https://artportalen.se/Sighting/135530615</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135530625</v>
+        <v>135530619</v>
       </c>
       <c r="B59" t="n">
-        <v>98196</v>
+        <v>57993</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>745727</v>
+        <v>745225</v>
       </c>
       <c r="R59" t="n">
-        <v>7200965</v>
+        <v>7201291</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7585,7 +7540,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7595,7 +7550,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7625,16 +7585,16 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530625</t>
+          <t>https://artportalen.se/Sighting/135530619</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135530568</v>
+        <v>135530575</v>
       </c>
       <c r="B60" t="n">
-        <v>79483</v>
+        <v>58154</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7642,34 +7602,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>260591</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>745105</v>
+        <v>745036</v>
       </c>
       <c r="R60" t="n">
-        <v>7201186</v>
+        <v>7201097</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7701,7 +7666,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7711,7 +7676,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7741,7 +7711,1081 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135530575</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135530581</v>
+      </c>
+      <c r="B61" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Finnboberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>745092</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7200970</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Läte</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135530581</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135530593</v>
+      </c>
+      <c r="B62" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Finnboberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>745345</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7200823</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Läten flera st</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135530593</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135530595</v>
+      </c>
+      <c r="B63" t="n">
+        <v>58154</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Finnboberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>745322</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7200832</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Läten</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135530595</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135530624</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98196</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Finnboberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>745746</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7200976</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135530624</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135530625</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98196</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Finnboberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>745727</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7200965</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135530625</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136735429</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98214</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Båtforsheden södra, Vb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>745701</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7200976</v>
+      </c>
+      <c r="S66" t="n">
+        <v>13</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735429</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136735434</v>
+      </c>
+      <c r="B67" t="n">
+        <v>91583</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Båtforsheden södra, Vb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>745585</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7201188</v>
+      </c>
+      <c r="S67" t="n">
+        <v>12</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735434</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135530568</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Finnboberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>745105</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7201186</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135530568</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136735428</v>
+      </c>
+      <c r="B69" t="n">
+        <v>90782</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6331677</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spökfransskivling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Ripartites borealis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>T.Ulvinen &amp; al.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Båtforsheden södra, Vb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>745701</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7200979</v>
+      </c>
+      <c r="S69" t="n">
+        <v>24</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735428</t>
         </is>
       </c>
     </row>
@@ -7806,6 +8850,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136735432</v>
       </c>
       <c r="B2" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136735435</v>
       </c>
       <c r="B3" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136735430</v>
       </c>
       <c r="B4" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>136735426</v>
       </c>
       <c r="B5" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>136735427</v>
       </c>
       <c r="B6" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136735433</v>
       </c>
       <c r="B7" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>136735429</v>
       </c>
       <c r="B66" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>136735434</v>
       </c>
       <c r="B67" t="n">
-        <v>91583</v>
+        <v>91585</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
         <v>136735428</v>
       </c>
       <c r="B69" t="n">
-        <v>90782</v>
+        <v>90784</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ69"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136735432</v>
+        <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>93403</v>
+        <v>87501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Båtforsheden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745633</v>
+        <v>745627</v>
       </c>
       <c r="R2" t="n">
-        <v>7201149</v>
+        <v>7201170</v>
       </c>
       <c r="S2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +778,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,38 +793,38 @@
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735432</t>
+          <t>https://artportalen.se/Sighting/136827667</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136735435</v>
+        <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,13 +834,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>745575</v>
+        <v>745633</v>
       </c>
       <c r="R3" t="n">
-        <v>7201201</v>
+        <v>7201149</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,16 +909,16 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735435</t>
+          <t>https://artportalen.se/Sighting/136735432</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136735430</v>
+        <v>136827664</v>
       </c>
       <c r="B4" t="n">
-        <v>93053</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,37 +926,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Båtforsheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745678</v>
+        <v>745702</v>
       </c>
       <c r="R4" t="n">
-        <v>7201079</v>
+        <v>7201119</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,12 +1013,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1022,16 +1028,16 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735430</t>
+          <t>https://artportalen.se/Sighting/136827664</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136735426</v>
+        <v>136735435</v>
       </c>
       <c r="B5" t="n">
-        <v>90893</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +1045,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,13 +1069,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745736</v>
+        <v>745575</v>
       </c>
       <c r="R5" t="n">
-        <v>7200987</v>
+        <v>7201201</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1098,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,16 +1144,16 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735426</t>
+          <t>https://artportalen.se/Sighting/136735435</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136735427</v>
+        <v>136827663</v>
       </c>
       <c r="B6" t="n">
-        <v>90893</v>
+        <v>93413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,37 +1161,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6286</v>
+        <v>4365</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Båtforsheden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745701</v>
+        <v>745702</v>
       </c>
       <c r="R6" t="n">
-        <v>7200979</v>
+        <v>7201121</v>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,12 +1248,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1254,38 +1263,38 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735427</t>
+          <t>https://artportalen.se/Sighting/136827663</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136735433</v>
+        <v>136735430</v>
       </c>
       <c r="B7" t="n">
-        <v>90893</v>
+        <v>93053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,13 +1304,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745611</v>
+        <v>745678</v>
       </c>
       <c r="R7" t="n">
-        <v>7201151</v>
+        <v>7201079</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,16 +1379,16 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735433</t>
+          <t>https://artportalen.se/Sighting/136735430</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135530557</v>
+        <v>136735426</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>90893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,37 +1396,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745289</v>
+        <v>745736</v>
       </c>
       <c r="R8" t="n">
-        <v>7201361</v>
+        <v>7200987</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,22 +1450,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,31 +1480,31 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530557</t>
+          <t>https://artportalen.se/Sighting/136735426</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135530558</v>
+        <v>136735427</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>90893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,37 +1512,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745276</v>
+        <v>745701</v>
       </c>
       <c r="R9" t="n">
-        <v>7201299</v>
+        <v>7200979</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,22 +1566,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,31 +1596,31 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530558</t>
+          <t>https://artportalen.se/Sighting/136735427</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135530559</v>
+        <v>136735433</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>90893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,37 +1628,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745236</v>
+        <v>745611</v>
       </c>
       <c r="R10" t="n">
-        <v>7201208</v>
+        <v>7201151</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1673,22 +1682,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,28 +1712,28 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530559</t>
+          <t>https://artportalen.se/Sighting/136735433</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135530567</v>
+        <v>135530557</v>
       </c>
       <c r="B11" t="n">
         <v>79460</v>
@@ -1759,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745105</v>
+        <v>745289</v>
       </c>
       <c r="R11" t="n">
-        <v>7201186</v>
+        <v>7201361</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,13 +1843,13 @@
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530567</t>
+          <t>https://artportalen.se/Sighting/135530557</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135530570</v>
+        <v>135530558</v>
       </c>
       <c r="B12" t="n">
         <v>79460</v>
@@ -1875,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745072</v>
+        <v>745276</v>
       </c>
       <c r="R12" t="n">
-        <v>7201155</v>
+        <v>7201299</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1910,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1950,13 +1959,13 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530570</t>
+          <t>https://artportalen.se/Sighting/135530558</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135530571</v>
+        <v>135530559</v>
       </c>
       <c r="B13" t="n">
         <v>79460</v>
@@ -1991,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745071</v>
+        <v>745236</v>
       </c>
       <c r="R13" t="n">
-        <v>7201129</v>
+        <v>7201208</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2035,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2045,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,13 +2075,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530571</t>
+          <t>https://artportalen.se/Sighting/135530559</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135530572</v>
+        <v>135530567</v>
       </c>
       <c r="B14" t="n">
         <v>79460</v>
@@ -2107,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745062</v>
+        <v>745105</v>
       </c>
       <c r="R14" t="n">
-        <v>7201112</v>
+        <v>7201186</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,13 +2191,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530572</t>
+          <t>https://artportalen.se/Sighting/135530567</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135530574</v>
+        <v>135530570</v>
       </c>
       <c r="B15" t="n">
         <v>79460</v>
@@ -2223,10 +2232,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745036</v>
+        <v>745072</v>
       </c>
       <c r="R15" t="n">
-        <v>7201097</v>
+        <v>7201155</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,13 +2307,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530574</t>
+          <t>https://artportalen.se/Sighting/135530570</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135530576</v>
+        <v>135530571</v>
       </c>
       <c r="B16" t="n">
         <v>79460</v>
@@ -2339,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745030</v>
+        <v>745071</v>
       </c>
       <c r="R16" t="n">
-        <v>7201106</v>
+        <v>7201129</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,13 +2423,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530576</t>
+          <t>https://artportalen.se/Sighting/135530571</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135530577</v>
+        <v>135530572</v>
       </c>
       <c r="B17" t="n">
         <v>79460</v>
@@ -2455,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>744996</v>
+        <v>745062</v>
       </c>
       <c r="R17" t="n">
-        <v>7201075</v>
+        <v>7201112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2530,13 +2539,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530577</t>
+          <t>https://artportalen.se/Sighting/135530572</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135530579</v>
+        <v>135530574</v>
       </c>
       <c r="B18" t="n">
         <v>79460</v>
@@ -2571,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745068</v>
+        <v>745036</v>
       </c>
       <c r="R18" t="n">
-        <v>7201004</v>
+        <v>7201097</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2606,7 +2615,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2625,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,13 +2655,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530579</t>
+          <t>https://artportalen.se/Sighting/135530574</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135530580</v>
+        <v>135530576</v>
       </c>
       <c r="B19" t="n">
         <v>79460</v>
@@ -2687,10 +2696,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745103</v>
+        <v>745030</v>
       </c>
       <c r="R19" t="n">
-        <v>7201015</v>
+        <v>7201106</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2722,7 +2731,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2732,7 +2741,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2762,13 +2771,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530580</t>
+          <t>https://artportalen.se/Sighting/135530576</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135530582</v>
+        <v>135530577</v>
       </c>
       <c r="B20" t="n">
         <v>79460</v>
@@ -2803,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>745109</v>
+        <v>744996</v>
       </c>
       <c r="R20" t="n">
-        <v>7200985</v>
+        <v>7201075</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2838,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,12 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Flera träd</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,13 +2887,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530582</t>
+          <t>https://artportalen.se/Sighting/135530577</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135530583</v>
+        <v>135530579</v>
       </c>
       <c r="B21" t="n">
         <v>79460</v>
@@ -2924,10 +2928,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745138</v>
+        <v>745068</v>
       </c>
       <c r="R21" t="n">
-        <v>7200924</v>
+        <v>7201004</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2959,7 +2963,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2969,7 +2973,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2999,13 +3003,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530583</t>
+          <t>https://artportalen.se/Sighting/135530579</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135530584</v>
+        <v>135530580</v>
       </c>
       <c r="B22" t="n">
         <v>79460</v>
@@ -3040,10 +3044,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745188</v>
+        <v>745103</v>
       </c>
       <c r="R22" t="n">
-        <v>7200877</v>
+        <v>7201015</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3075,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3085,7 +3089,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,13 +3119,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530584</t>
+          <t>https://artportalen.se/Sighting/135530580</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135530585</v>
+        <v>135530582</v>
       </c>
       <c r="B23" t="n">
         <v>79460</v>
@@ -3156,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745178</v>
+        <v>745109</v>
       </c>
       <c r="R23" t="n">
-        <v>7200888</v>
+        <v>7200985</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,7 +3195,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,12 +3205,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3236,13 +3240,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530585</t>
+          <t>https://artportalen.se/Sighting/135530582</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135530586</v>
+        <v>135530583</v>
       </c>
       <c r="B24" t="n">
         <v>79460</v>
@@ -3277,10 +3281,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745241</v>
+        <v>745138</v>
       </c>
       <c r="R24" t="n">
-        <v>7200789</v>
+        <v>7200924</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3312,7 +3316,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3322,7 +3326,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3352,13 +3356,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530586</t>
+          <t>https://artportalen.se/Sighting/135530583</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135530587</v>
+        <v>135530584</v>
       </c>
       <c r="B25" t="n">
         <v>79460</v>
@@ -3393,10 +3397,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745339</v>
+        <v>745188</v>
       </c>
       <c r="R25" t="n">
-        <v>7200794</v>
+        <v>7200877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3428,7 +3432,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3438,7 +3442,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3468,13 +3472,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530587</t>
+          <t>https://artportalen.se/Sighting/135530584</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135530592</v>
+        <v>135530585</v>
       </c>
       <c r="B26" t="n">
         <v>79460</v>
@@ -3509,10 +3513,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745345</v>
+        <v>745178</v>
       </c>
       <c r="R26" t="n">
-        <v>7200823</v>
+        <v>7200888</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3544,7 +3548,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3554,7 +3558,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3584,13 +3593,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530592</t>
+          <t>https://artportalen.se/Sighting/135530585</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135530594</v>
+        <v>135530586</v>
       </c>
       <c r="B27" t="n">
         <v>79460</v>
@@ -3625,10 +3634,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745322</v>
+        <v>745241</v>
       </c>
       <c r="R27" t="n">
-        <v>7200832</v>
+        <v>7200789</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3660,7 +3669,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3670,7 +3679,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3700,13 +3709,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530594</t>
+          <t>https://artportalen.se/Sighting/135530586</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135530596</v>
+        <v>135530587</v>
       </c>
       <c r="B28" t="n">
         <v>79460</v>
@@ -3735,19 +3744,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745314</v>
+        <v>745339</v>
       </c>
       <c r="R28" t="n">
-        <v>7200859</v>
+        <v>7200794</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3779,7 +3785,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3789,7 +3795,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3798,7 +3804,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3820,13 +3825,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530596</t>
+          <t>https://artportalen.se/Sighting/135530587</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135530603</v>
+        <v>135530592</v>
       </c>
       <c r="B29" t="n">
         <v>79460</v>
@@ -3861,10 +3866,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745329</v>
+        <v>745345</v>
       </c>
       <c r="R29" t="n">
-        <v>7200907</v>
+        <v>7200823</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3896,7 +3901,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3906,12 +3911,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3941,13 +3941,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530603</t>
+          <t>https://artportalen.se/Sighting/135530592</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135530604</v>
+        <v>135530594</v>
       </c>
       <c r="B30" t="n">
         <v>79460</v>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745301</v>
+        <v>745322</v>
       </c>
       <c r="R30" t="n">
-        <v>7200917</v>
+        <v>7200832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4027,12 +4027,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Bilder</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4062,13 +4057,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530604</t>
+          <t>https://artportalen.se/Sighting/135530594</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135530606</v>
+        <v>135530596</v>
       </c>
       <c r="B31" t="n">
         <v>79460</v>
@@ -4097,16 +4092,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745315</v>
+        <v>745314</v>
       </c>
       <c r="R31" t="n">
-        <v>7200949</v>
+        <v>7200859</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4138,7 +4136,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4148,7 +4146,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4157,6 +4155,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4178,13 +4177,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530606</t>
+          <t>https://artportalen.se/Sighting/135530596</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135530607</v>
+        <v>135530603</v>
       </c>
       <c r="B32" t="n">
         <v>79460</v>
@@ -4219,10 +4218,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745287</v>
+        <v>745329</v>
       </c>
       <c r="R32" t="n">
-        <v>7200957</v>
+        <v>7200907</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4254,7 +4253,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4264,7 +4263,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4299,13 +4298,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530607</t>
+          <t>https://artportalen.se/Sighting/135530603</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135530611</v>
+        <v>135530604</v>
       </c>
       <c r="B33" t="n">
         <v>79460</v>
@@ -4340,10 +4339,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745294</v>
+        <v>745301</v>
       </c>
       <c r="R33" t="n">
-        <v>7201009</v>
+        <v>7200917</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4375,7 +4374,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4385,7 +4384,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4415,13 +4419,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530611</t>
+          <t>https://artportalen.se/Sighting/135530604</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135530616</v>
+        <v>135530606</v>
       </c>
       <c r="B34" t="n">
         <v>79460</v>
@@ -4456,10 +4460,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745272</v>
+        <v>745315</v>
       </c>
       <c r="R34" t="n">
-        <v>7201118</v>
+        <v>7200949</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4491,7 +4495,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4501,7 +4505,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4531,13 +4535,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530616</t>
+          <t>https://artportalen.se/Sighting/135530606</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135530617</v>
+        <v>135530607</v>
       </c>
       <c r="B35" t="n">
         <v>79460</v>
@@ -4572,10 +4576,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745239</v>
+        <v>745287</v>
       </c>
       <c r="R35" t="n">
-        <v>7201178</v>
+        <v>7200957</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4607,7 +4611,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4617,7 +4621,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4647,13 +4656,13 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530617</t>
+          <t>https://artportalen.se/Sighting/135530607</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135530618</v>
+        <v>135530611</v>
       </c>
       <c r="B36" t="n">
         <v>79460</v>
@@ -4688,10 +4697,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745225</v>
+        <v>745294</v>
       </c>
       <c r="R36" t="n">
-        <v>7201291</v>
+        <v>7201009</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4723,7 +4732,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4733,7 +4742,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4763,13 +4772,13 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530618</t>
+          <t>https://artportalen.se/Sighting/135530611</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135530626</v>
+        <v>135530616</v>
       </c>
       <c r="B37" t="n">
         <v>79460</v>
@@ -4804,10 +4813,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745686</v>
+        <v>745272</v>
       </c>
       <c r="R37" t="n">
-        <v>7200954</v>
+        <v>7201118</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4839,7 +4848,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4849,7 +4858,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4879,38 +4888,38 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530626</t>
+          <t>https://artportalen.se/Sighting/135530616</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135530578</v>
+        <v>135530617</v>
       </c>
       <c r="B38" t="n">
-        <v>78863</v>
+        <v>79460</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4920,10 +4929,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745042</v>
+        <v>745239</v>
       </c>
       <c r="R38" t="n">
-        <v>7201067</v>
+        <v>7201178</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4955,7 +4964,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4965,7 +4974,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4995,38 +5004,38 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530578</t>
+          <t>https://artportalen.se/Sighting/135530617</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135530560</v>
+        <v>135530618</v>
       </c>
       <c r="B39" t="n">
-        <v>79217</v>
+        <v>79460</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5036,10 +5045,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745246</v>
+        <v>745225</v>
       </c>
       <c r="R39" t="n">
-        <v>7201169</v>
+        <v>7201291</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5071,7 +5080,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5081,7 +5090,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5111,38 +5120,38 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530560</t>
+          <t>https://artportalen.se/Sighting/135530618</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135530598</v>
+        <v>135530626</v>
       </c>
       <c r="B40" t="n">
-        <v>80575</v>
+        <v>79460</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5152,10 +5161,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745329</v>
+        <v>745686</v>
       </c>
       <c r="R40" t="n">
-        <v>7200885</v>
+        <v>7200954</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5187,7 +5196,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5197,7 +5206,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5227,16 +5236,16 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530598</t>
+          <t>https://artportalen.se/Sighting/135530626</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135530608</v>
+        <v>135530578</v>
       </c>
       <c r="B41" t="n">
-        <v>80575</v>
+        <v>78863</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5244,21 +5253,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5268,10 +5277,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745270</v>
+        <v>745042</v>
       </c>
       <c r="R41" t="n">
-        <v>7200986</v>
+        <v>7201067</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5303,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5313,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5343,16 +5352,16 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530608</t>
+          <t>https://artportalen.se/Sighting/135530578</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135530613</v>
+        <v>135530560</v>
       </c>
       <c r="B42" t="n">
-        <v>80575</v>
+        <v>79217</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5360,21 +5369,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5384,10 +5393,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745318</v>
+        <v>745246</v>
       </c>
       <c r="R42" t="n">
-        <v>7201025</v>
+        <v>7201169</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5419,7 +5428,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5429,12 +5438,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5464,38 +5468,38 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530613</t>
+          <t>https://artportalen.se/Sighting/135530560</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135530599</v>
+        <v>135530598</v>
       </c>
       <c r="B43" t="n">
-        <v>80580</v>
+        <v>80575</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5505,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745333</v>
+        <v>745329</v>
       </c>
       <c r="R43" t="n">
-        <v>7200883</v>
+        <v>7200885</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5580,38 +5584,38 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530599</t>
+          <t>https://artportalen.se/Sighting/135530598</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135530600</v>
+        <v>135530608</v>
       </c>
       <c r="B44" t="n">
-        <v>80586</v>
+        <v>80575</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5621,10 +5625,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745333</v>
+        <v>745270</v>
       </c>
       <c r="R44" t="n">
-        <v>7200883</v>
+        <v>7200986</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5656,7 +5660,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5666,7 +5670,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5696,38 +5700,38 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530600</t>
+          <t>https://artportalen.se/Sighting/135530608</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135530609</v>
+        <v>135530613</v>
       </c>
       <c r="B45" t="n">
-        <v>80586</v>
+        <v>80575</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5737,10 +5741,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745276</v>
+        <v>745318</v>
       </c>
       <c r="R45" t="n">
-        <v>7200976</v>
+        <v>7201025</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5772,7 +5776,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5782,7 +5786,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5812,56 +5821,51 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530609</t>
+          <t>https://artportalen.se/Sighting/135530613</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135530562</v>
+        <v>135530599</v>
       </c>
       <c r="B46" t="n">
-        <v>57993</v>
+        <v>80580</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745221</v>
+        <v>745333</v>
       </c>
       <c r="R46" t="n">
-        <v>7201177</v>
+        <v>7200883</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5893,7 +5897,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5903,12 +5907,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bikder</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5938,56 +5937,51 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530562</t>
+          <t>https://artportalen.se/Sighting/135530599</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135530563</v>
+        <v>135530600</v>
       </c>
       <c r="B47" t="n">
-        <v>57993</v>
+        <v>80586</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745147</v>
+        <v>745333</v>
       </c>
       <c r="R47" t="n">
-        <v>7201197</v>
+        <v>7200883</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6019,7 +6013,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6029,12 +6023,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bilder</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6064,56 +6053,51 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530563</t>
+          <t>https://artportalen.se/Sighting/135530600</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135530564</v>
+        <v>135530609</v>
       </c>
       <c r="B48" t="n">
-        <v>57993</v>
+        <v>80586</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745132</v>
+        <v>745276</v>
       </c>
       <c r="R48" t="n">
-        <v>7201209</v>
+        <v>7200976</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6145,7 +6129,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6155,12 +6139,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6190,13 +6169,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530564</t>
+          <t>https://artportalen.se/Sighting/135530609</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135530565</v>
+        <v>135530562</v>
       </c>
       <c r="B49" t="n">
         <v>57993</v>
@@ -6227,7 +6206,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6236,10 +6215,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745109</v>
+        <v>745221</v>
       </c>
       <c r="R49" t="n">
-        <v>7201209</v>
+        <v>7201177</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6271,7 +6250,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6281,12 +6260,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack bikder</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6316,13 +6295,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530565</t>
+          <t>https://artportalen.se/Sighting/135530562</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135530566</v>
+        <v>135530563</v>
       </c>
       <c r="B50" t="n">
         <v>57993</v>
@@ -6362,10 +6341,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745100</v>
+        <v>745147</v>
       </c>
       <c r="R50" t="n">
-        <v>7201200</v>
+        <v>7201197</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6397,7 +6376,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6407,12 +6386,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack bilder</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6442,13 +6421,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530566</t>
+          <t>https://artportalen.se/Sighting/135530563</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135530573</v>
+        <v>135530564</v>
       </c>
       <c r="B51" t="n">
         <v>57993</v>
@@ -6479,7 +6458,7 @@
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6488,10 +6467,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>745046</v>
+        <v>745132</v>
       </c>
       <c r="R51" t="n">
-        <v>7201117</v>
+        <v>7201209</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,7 +6502,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6533,12 +6512,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack bilder</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6568,13 +6547,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530573</t>
+          <t>https://artportalen.se/Sighting/135530564</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135530588</v>
+        <v>135530565</v>
       </c>
       <c r="B52" t="n">
         <v>57993</v>
@@ -6603,24 +6582,21 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>745362</v>
+        <v>745109</v>
       </c>
       <c r="R52" t="n">
-        <v>7200804</v>
+        <v>7201209</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6652,7 +6628,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6662,7 +6638,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6697,13 +6673,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530588</t>
+          <t>https://artportalen.se/Sighting/135530565</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135530590</v>
+        <v>135530566</v>
       </c>
       <c r="B53" t="n">
         <v>57993</v>
@@ -6743,10 +6719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>745376</v>
+        <v>745100</v>
       </c>
       <c r="R53" t="n">
-        <v>7200807</v>
+        <v>7201200</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6778,7 +6754,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6788,12 +6764,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack bild</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6823,13 +6799,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530590</t>
+          <t>https://artportalen.se/Sighting/135530566</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135530605</v>
+        <v>135530573</v>
       </c>
       <c r="B54" t="n">
         <v>57993</v>
@@ -6858,24 +6834,21 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>745287</v>
+        <v>745046</v>
       </c>
       <c r="R54" t="n">
-        <v>7200930</v>
+        <v>7201117</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6907,7 +6880,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6917,19 +6890,19 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Skalad gran</t>
+          <t>Färska ringhack bilder</t>
         </is>
       </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -6952,13 +6925,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530605</t>
+          <t>https://artportalen.se/Sighting/135530573</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135530610</v>
+        <v>135530588</v>
       </c>
       <c r="B55" t="n">
         <v>57993</v>
@@ -7001,10 +6974,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>745278</v>
+        <v>745362</v>
       </c>
       <c r="R55" t="n">
-        <v>7201005</v>
+        <v>7200804</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7036,7 +7009,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7046,12 +7019,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska (?) ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7081,13 +7054,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530610</t>
+          <t>https://artportalen.se/Sighting/135530588</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135530612</v>
+        <v>135530590</v>
       </c>
       <c r="B56" t="n">
         <v>57993</v>
@@ -7118,7 +7091,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7127,10 +7100,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>745307</v>
+        <v>745376</v>
       </c>
       <c r="R56" t="n">
-        <v>7201037</v>
+        <v>7200807</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7162,7 +7135,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7172,12 +7145,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7207,13 +7180,13 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530612</t>
+          <t>https://artportalen.se/Sighting/135530590</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135530614</v>
+        <v>135530605</v>
       </c>
       <c r="B57" t="n">
         <v>57993</v>
@@ -7242,21 +7215,24 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>745306</v>
+        <v>745287</v>
       </c>
       <c r="R57" t="n">
-        <v>7201046</v>
+        <v>7200930</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7288,7 +7264,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7298,19 +7274,19 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Färska ringhack bild</t>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG57" t="b">
         <v>0</v>
@@ -7333,13 +7309,13 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530614</t>
+          <t>https://artportalen.se/Sighting/135530605</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135530615</v>
+        <v>135530610</v>
       </c>
       <c r="B58" t="n">
         <v>57993</v>
@@ -7368,21 +7344,24 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>745282</v>
+        <v>745278</v>
       </c>
       <c r="R58" t="n">
-        <v>7201100</v>
+        <v>7201005</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7414,7 +7393,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7424,12 +7403,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack bild</t>
+          <t>Färska (?) ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7459,13 +7438,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530615</t>
+          <t>https://artportalen.se/Sighting/135530610</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135530619</v>
+        <v>135530612</v>
       </c>
       <c r="B59" t="n">
         <v>57993</v>
@@ -7496,7 +7475,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7505,10 +7484,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>745225</v>
+        <v>745307</v>
       </c>
       <c r="R59" t="n">
-        <v>7201291</v>
+        <v>7201037</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7540,7 +7519,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7550,12 +7529,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7585,16 +7564,16 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530619</t>
+          <t>https://artportalen.se/Sighting/135530612</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135530575</v>
+        <v>135530614</v>
       </c>
       <c r="B60" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7602,27 +7581,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7631,10 +7610,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>745036</v>
+        <v>745306</v>
       </c>
       <c r="R60" t="n">
-        <v>7201097</v>
+        <v>7201046</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7666,7 +7645,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7676,12 +7655,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7711,16 +7690,16 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530575</t>
+          <t>https://artportalen.se/Sighting/135530614</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135530581</v>
+        <v>135530615</v>
       </c>
       <c r="B61" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7728,27 +7707,27 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7757,10 +7736,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>745092</v>
+        <v>745282</v>
       </c>
       <c r="R61" t="n">
-        <v>7200970</v>
+        <v>7201100</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7792,7 +7771,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7802,12 +7781,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7837,16 +7816,16 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530581</t>
+          <t>https://artportalen.se/Sighting/135530615</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135530593</v>
+        <v>135530619</v>
       </c>
       <c r="B62" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7854,27 +7833,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7883,10 +7862,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>745345</v>
+        <v>745225</v>
       </c>
       <c r="R62" t="n">
-        <v>7200823</v>
+        <v>7201291</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7918,7 +7897,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7928,12 +7907,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Läten flera st</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7963,13 +7942,13 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530593</t>
+          <t>https://artportalen.se/Sighting/135530619</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135530595</v>
+        <v>135530575</v>
       </c>
       <c r="B63" t="n">
         <v>58154</v>
@@ -8009,10 +7988,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>745322</v>
+        <v>745036</v>
       </c>
       <c r="R63" t="n">
-        <v>7200832</v>
+        <v>7201097</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8044,7 +8023,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8054,12 +8033,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Läten</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8089,51 +8068,56 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530595</t>
+          <t>https://artportalen.se/Sighting/135530575</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135530624</v>
+        <v>135530581</v>
       </c>
       <c r="B64" t="n">
-        <v>98196</v>
+        <v>58154</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>745746</v>
+        <v>745092</v>
       </c>
       <c r="R64" t="n">
-        <v>7200976</v>
+        <v>7200970</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8165,7 +8149,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8175,7 +8159,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8205,51 +8194,56 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530624</t>
+          <t>https://artportalen.se/Sighting/135530581</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135530625</v>
+        <v>135530593</v>
       </c>
       <c r="B65" t="n">
-        <v>98196</v>
+        <v>58154</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>745727</v>
+        <v>745345</v>
       </c>
       <c r="R65" t="n">
-        <v>7200965</v>
+        <v>7200823</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8281,7 +8275,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8291,7 +8285,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Läten flera st</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8321,54 +8320,59 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530625</t>
+          <t>https://artportalen.se/Sighting/135530593</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136735429</v>
+        <v>135530595</v>
       </c>
       <c r="B66" t="n">
-        <v>98219</v>
+        <v>58154</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>745701</v>
+        <v>745322</v>
       </c>
       <c r="R66" t="n">
-        <v>7200976</v>
+        <v>7200832</v>
       </c>
       <c r="S66" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8392,22 +8396,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Läten</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8422,69 +8431,69 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>Boreala Svampskogar</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735429</t>
+          <t>https://artportalen.se/Sighting/135530595</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136735434</v>
+        <v>135530624</v>
       </c>
       <c r="B67" t="n">
-        <v>91585</v>
+        <v>98196</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>256703</v>
+        <v>221941</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>745585</v>
+        <v>745746</v>
       </c>
       <c r="R67" t="n">
-        <v>7201188</v>
+        <v>7200976</v>
       </c>
       <c r="S67" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8508,22 +8517,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8538,53 +8547,53 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>Boreala Svampskogar</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735434</t>
+          <t>https://artportalen.se/Sighting/135530624</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135530568</v>
+        <v>135530625</v>
       </c>
       <c r="B68" t="n">
-        <v>79483</v>
+        <v>98196</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>260591</v>
+        <v>221941</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8594,10 +8603,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>745105</v>
+        <v>745727</v>
       </c>
       <c r="R68" t="n">
-        <v>7201186</v>
+        <v>7200965</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8629,7 +8638,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8639,7 +8648,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8669,38 +8678,38 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530568</t>
+          <t>https://artportalen.se/Sighting/135530625</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136735428</v>
+        <v>136735429</v>
       </c>
       <c r="B69" t="n">
-        <v>90784</v>
+        <v>98219</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6331677</v>
+        <v>221941</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spökfransskivling</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ripartites borealis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>T.Ulvinen &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8713,10 +8722,10 @@
         <v>745701</v>
       </c>
       <c r="R69" t="n">
-        <v>7200979</v>
+        <v>7200976</v>
       </c>
       <c r="S69" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8784,6 +8793,473 @@
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735429</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136827662</v>
+      </c>
+      <c r="B70" t="n">
+        <v>93440</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Båtforsheden, Vb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>745702</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7201121</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Petra Wikström</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136827662</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136735434</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91585</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Båtforsheden södra, Vb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>745585</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7201188</v>
+      </c>
+      <c r="S71" t="n">
+        <v>12</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735434</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135530568</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Finnboberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>745105</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7201186</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135530568</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136735428</v>
+      </c>
+      <c r="B73" t="n">
+        <v>90784</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6331677</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Spökfransskivling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ripartites borealis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>T.Ulvinen &amp; al.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Båtforsheden södra, Vb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>745701</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7200979</v>
+      </c>
+      <c r="S73" t="n">
+        <v>24</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136735428</t>
         </is>
@@ -8859,6 +9335,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ73"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136827664</v>
+        <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,37 +926,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Båtforsheden, Vb</t>
+          <t>Båtforsheden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>745702</v>
+        <v>745621</v>
       </c>
       <c r="R4" t="n">
-        <v>7201119</v>
+        <v>7201189</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,12 +1010,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1028,51 +1025,54 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827664</t>
+          <t>https://artportalen.se/Sighting/136835604</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136735435</v>
+        <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93409</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Båtforsheden, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>745575</v>
+        <v>745702</v>
       </c>
       <c r="R5" t="n">
-        <v>7201201</v>
+        <v>7201119</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,12 +1129,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1144,13 +1144,13 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735435</t>
+          <t>https://artportalen.se/Sighting/136827664</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136827663</v>
+        <v>136735435</v>
       </c>
       <c r="B6" t="n">
         <v>93413</v>
@@ -1179,19 +1179,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Båtforsheden, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>745702</v>
+        <v>745575</v>
       </c>
       <c r="R6" t="n">
-        <v>7201121</v>
+        <v>7201201</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,12 +1245,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1263,54 +1260,57 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827663</t>
+          <t>https://artportalen.se/Sighting/136735435</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136735430</v>
+        <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93053</v>
+        <v>93413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4745</v>
+        <v>4365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Båtforsheden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>745678</v>
+        <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201079</v>
+        <v>7201121</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,12 +1364,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1379,38 +1379,38 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735430</t>
+          <t>https://artportalen.se/Sighting/136827663</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136735426</v>
+        <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>90893</v>
+        <v>93053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6286</v>
+        <v>4745</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1420,13 +1420,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>745736</v>
+        <v>745678</v>
       </c>
       <c r="R8" t="n">
-        <v>7200987</v>
+        <v>7201079</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,16 +1495,16 @@
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735426</t>
+          <t>https://artportalen.se/Sighting/136735430</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136735427</v>
+        <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>90893</v>
+        <v>93395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,37 +1512,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6286</v>
+        <v>6055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Båtforsheden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>745701</v>
+        <v>745688</v>
       </c>
       <c r="R9" t="n">
-        <v>7200979</v>
+        <v>7201101</v>
       </c>
       <c r="S9" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,12 +1596,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1611,13 +1611,13 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735427</t>
+          <t>https://artportalen.se/Sighting/136835603</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136735433</v>
+        <v>136735426</v>
       </c>
       <c r="B10" t="n">
         <v>90893</v>
@@ -1652,13 +1652,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>745611</v>
+        <v>745736</v>
       </c>
       <c r="R10" t="n">
-        <v>7201151</v>
+        <v>7200987</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,16 +1727,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735433</t>
+          <t>https://artportalen.se/Sighting/136735426</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135530557</v>
+        <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>79460</v>
+        <v>90893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,37 +1744,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>745289</v>
+        <v>745701</v>
       </c>
       <c r="R11" t="n">
-        <v>7201361</v>
+        <v>7200979</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,22 +1798,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,31 +1828,31 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530557</t>
+          <t>https://artportalen.se/Sighting/136735427</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135530558</v>
+        <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>79460</v>
+        <v>90893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,37 +1860,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden södra, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>745276</v>
+        <v>745611</v>
       </c>
       <c r="R12" t="n">
-        <v>7201299</v>
+        <v>7201151</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1914,22 +1914,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,28 +1944,28 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530558</t>
+          <t>https://artportalen.se/Sighting/136735433</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135530559</v>
+        <v>135530557</v>
       </c>
       <c r="B13" t="n">
         <v>79460</v>
@@ -2000,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>745236</v>
+        <v>745289</v>
       </c>
       <c r="R13" t="n">
-        <v>7201208</v>
+        <v>7201361</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,13 +2075,13 @@
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530559</t>
+          <t>https://artportalen.se/Sighting/135530557</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135530567</v>
+        <v>135530558</v>
       </c>
       <c r="B14" t="n">
         <v>79460</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>745105</v>
+        <v>745276</v>
       </c>
       <c r="R14" t="n">
-        <v>7201186</v>
+        <v>7201299</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,13 +2191,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530567</t>
+          <t>https://artportalen.se/Sighting/135530558</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135530570</v>
+        <v>135530559</v>
       </c>
       <c r="B15" t="n">
         <v>79460</v>
@@ -2232,10 +2232,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>745072</v>
+        <v>745236</v>
       </c>
       <c r="R15" t="n">
-        <v>7201155</v>
+        <v>7201208</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,13 +2307,13 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530570</t>
+          <t>https://artportalen.se/Sighting/135530559</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135530571</v>
+        <v>135530567</v>
       </c>
       <c r="B16" t="n">
         <v>79460</v>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>745071</v>
+        <v>745105</v>
       </c>
       <c r="R16" t="n">
-        <v>7201129</v>
+        <v>7201186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2423,13 +2423,13 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530571</t>
+          <t>https://artportalen.se/Sighting/135530567</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135530572</v>
+        <v>135530570</v>
       </c>
       <c r="B17" t="n">
         <v>79460</v>
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>745062</v>
+        <v>745072</v>
       </c>
       <c r="R17" t="n">
-        <v>7201112</v>
+        <v>7201155</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2539,13 +2539,13 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530572</t>
+          <t>https://artportalen.se/Sighting/135530570</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135530574</v>
+        <v>135530571</v>
       </c>
       <c r="B18" t="n">
         <v>79460</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>745036</v>
+        <v>745071</v>
       </c>
       <c r="R18" t="n">
-        <v>7201097</v>
+        <v>7201129</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2655,13 +2655,13 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530574</t>
+          <t>https://artportalen.se/Sighting/135530571</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135530576</v>
+        <v>135530572</v>
       </c>
       <c r="B19" t="n">
         <v>79460</v>
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>745030</v>
+        <v>745062</v>
       </c>
       <c r="R19" t="n">
-        <v>7201106</v>
+        <v>7201112</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,13 +2771,13 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530576</t>
+          <t>https://artportalen.se/Sighting/135530572</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135530577</v>
+        <v>135530574</v>
       </c>
       <c r="B20" t="n">
         <v>79460</v>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>744996</v>
+        <v>745036</v>
       </c>
       <c r="R20" t="n">
-        <v>7201075</v>
+        <v>7201097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,13 +2887,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530577</t>
+          <t>https://artportalen.se/Sighting/135530574</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135530579</v>
+        <v>135530576</v>
       </c>
       <c r="B21" t="n">
         <v>79460</v>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>745068</v>
+        <v>745030</v>
       </c>
       <c r="R21" t="n">
-        <v>7201004</v>
+        <v>7201106</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3003,13 +3003,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530579</t>
+          <t>https://artportalen.se/Sighting/135530576</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135530580</v>
+        <v>135530577</v>
       </c>
       <c r="B22" t="n">
         <v>79460</v>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>745103</v>
+        <v>744996</v>
       </c>
       <c r="R22" t="n">
-        <v>7201015</v>
+        <v>7201075</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3119,13 +3119,13 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530580</t>
+          <t>https://artportalen.se/Sighting/135530577</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135530582</v>
+        <v>135530579</v>
       </c>
       <c r="B23" t="n">
         <v>79460</v>
@@ -3160,10 +3160,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>745109</v>
+        <v>745068</v>
       </c>
       <c r="R23" t="n">
-        <v>7200985</v>
+        <v>7201004</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3205,12 +3205,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Flera träd</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,13 +3235,13 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530582</t>
+          <t>https://artportalen.se/Sighting/135530579</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135530583</v>
+        <v>135530580</v>
       </c>
       <c r="B24" t="n">
         <v>79460</v>
@@ -3281,10 +3276,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>745138</v>
+        <v>745103</v>
       </c>
       <c r="R24" t="n">
-        <v>7200924</v>
+        <v>7201015</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3316,7 +3311,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3326,7 +3321,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3356,13 +3351,13 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530583</t>
+          <t>https://artportalen.se/Sighting/135530580</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135530584</v>
+        <v>135530582</v>
       </c>
       <c r="B25" t="n">
         <v>79460</v>
@@ -3397,10 +3392,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>745188</v>
+        <v>745109</v>
       </c>
       <c r="R25" t="n">
-        <v>7200877</v>
+        <v>7200985</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3432,7 +3427,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3442,7 +3437,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Flera träd</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3472,13 +3472,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530584</t>
+          <t>https://artportalen.se/Sighting/135530582</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135530585</v>
+        <v>135530583</v>
       </c>
       <c r="B26" t="n">
         <v>79460</v>
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>745178</v>
+        <v>745138</v>
       </c>
       <c r="R26" t="n">
-        <v>7200888</v>
+        <v>7200924</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3558,12 +3558,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,13 +3588,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530585</t>
+          <t>https://artportalen.se/Sighting/135530583</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135530586</v>
+        <v>135530584</v>
       </c>
       <c r="B27" t="n">
         <v>79460</v>
@@ -3634,10 +3629,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>745241</v>
+        <v>745188</v>
       </c>
       <c r="R27" t="n">
-        <v>7200789</v>
+        <v>7200877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3669,7 +3664,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3679,7 +3674,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3709,13 +3704,13 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530586</t>
+          <t>https://artportalen.se/Sighting/135530584</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135530587</v>
+        <v>135530585</v>
       </c>
       <c r="B28" t="n">
         <v>79460</v>
@@ -3750,10 +3745,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>745339</v>
+        <v>745178</v>
       </c>
       <c r="R28" t="n">
-        <v>7200794</v>
+        <v>7200888</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3785,7 +3780,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3795,7 +3790,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3825,13 +3825,13 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530587</t>
+          <t>https://artportalen.se/Sighting/135530585</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135530592</v>
+        <v>135530586</v>
       </c>
       <c r="B29" t="n">
         <v>79460</v>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>745345</v>
+        <v>745241</v>
       </c>
       <c r="R29" t="n">
-        <v>7200823</v>
+        <v>7200789</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3941,13 +3941,13 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530592</t>
+          <t>https://artportalen.se/Sighting/135530586</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135530594</v>
+        <v>135530587</v>
       </c>
       <c r="B30" t="n">
         <v>79460</v>
@@ -3982,10 +3982,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>745322</v>
+        <v>745339</v>
       </c>
       <c r="R30" t="n">
-        <v>7200832</v>
+        <v>7200794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4017,7 +4017,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4057,13 +4057,13 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530594</t>
+          <t>https://artportalen.se/Sighting/135530587</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135530596</v>
+        <v>135530592</v>
       </c>
       <c r="B31" t="n">
         <v>79460</v>
@@ -4092,19 +4092,16 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>745314</v>
+        <v>745345</v>
       </c>
       <c r="R31" t="n">
-        <v>7200859</v>
+        <v>7200823</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4136,7 +4133,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4146,7 +4143,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4155,7 +4152,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4177,13 +4173,13 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530596</t>
+          <t>https://artportalen.se/Sighting/135530592</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135530603</v>
+        <v>135530594</v>
       </c>
       <c r="B32" t="n">
         <v>79460</v>
@@ -4218,10 +4214,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>745329</v>
+        <v>745322</v>
       </c>
       <c r="R32" t="n">
-        <v>7200907</v>
+        <v>7200832</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4253,7 +4249,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4263,12 +4259,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:55</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4298,13 +4289,13 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530603</t>
+          <t>https://artportalen.se/Sighting/135530594</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135530604</v>
+        <v>135530596</v>
       </c>
       <c r="B33" t="n">
         <v>79460</v>
@@ -4333,16 +4324,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>745301</v>
+        <v>745314</v>
       </c>
       <c r="R33" t="n">
-        <v>7200917</v>
+        <v>7200859</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4374,7 +4368,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4384,12 +4378,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:57</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Bilder</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4398,6 +4387,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4419,13 +4409,13 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530604</t>
+          <t>https://artportalen.se/Sighting/135530596</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135530606</v>
+        <v>135530603</v>
       </c>
       <c r="B34" t="n">
         <v>79460</v>
@@ -4460,10 +4450,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>745315</v>
+        <v>745329</v>
       </c>
       <c r="R34" t="n">
-        <v>7200949</v>
+        <v>7200907</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4495,7 +4485,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4505,7 +4495,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4535,13 +4530,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530606</t>
+          <t>https://artportalen.se/Sighting/135530603</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135530607</v>
+        <v>135530604</v>
       </c>
       <c r="B35" t="n">
         <v>79460</v>
@@ -4576,10 +4571,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>745287</v>
+        <v>745301</v>
       </c>
       <c r="R35" t="n">
-        <v>7200957</v>
+        <v>7200917</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4611,7 +4606,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4621,12 +4616,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4656,13 +4651,13 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530607</t>
+          <t>https://artportalen.se/Sighting/135530604</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135530611</v>
+        <v>135530606</v>
       </c>
       <c r="B36" t="n">
         <v>79460</v>
@@ -4697,10 +4692,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>745294</v>
+        <v>745315</v>
       </c>
       <c r="R36" t="n">
-        <v>7201009</v>
+        <v>7200949</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4732,7 +4727,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4742,7 +4737,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4772,13 +4767,13 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530611</t>
+          <t>https://artportalen.se/Sighting/135530606</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135530616</v>
+        <v>135530607</v>
       </c>
       <c r="B37" t="n">
         <v>79460</v>
@@ -4813,10 +4808,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>745272</v>
+        <v>745287</v>
       </c>
       <c r="R37" t="n">
-        <v>7201118</v>
+        <v>7200957</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4848,7 +4843,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4858,7 +4853,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4888,13 +4888,13 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530616</t>
+          <t>https://artportalen.se/Sighting/135530607</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135530617</v>
+        <v>135530611</v>
       </c>
       <c r="B38" t="n">
         <v>79460</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>745239</v>
+        <v>745294</v>
       </c>
       <c r="R38" t="n">
-        <v>7201178</v>
+        <v>7201009</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5004,13 +5004,13 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530617</t>
+          <t>https://artportalen.se/Sighting/135530611</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135530618</v>
+        <v>135530616</v>
       </c>
       <c r="B39" t="n">
         <v>79460</v>
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>745225</v>
+        <v>745272</v>
       </c>
       <c r="R39" t="n">
-        <v>7201291</v>
+        <v>7201118</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5120,13 +5120,13 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530618</t>
+          <t>https://artportalen.se/Sighting/135530616</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135530626</v>
+        <v>135530617</v>
       </c>
       <c r="B40" t="n">
         <v>79460</v>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>745686</v>
+        <v>745239</v>
       </c>
       <c r="R40" t="n">
-        <v>7200954</v>
+        <v>7201178</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5236,38 +5236,38 @@
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530626</t>
+          <t>https://artportalen.se/Sighting/135530617</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135530578</v>
+        <v>135530618</v>
       </c>
       <c r="B41" t="n">
-        <v>78863</v>
+        <v>79460</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>745042</v>
+        <v>745225</v>
       </c>
       <c r="R41" t="n">
-        <v>7201067</v>
+        <v>7201291</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5352,38 +5352,38 @@
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530578</t>
+          <t>https://artportalen.se/Sighting/135530618</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135530560</v>
+        <v>135530626</v>
       </c>
       <c r="B42" t="n">
-        <v>79217</v>
+        <v>79460</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5393,10 +5393,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>745246</v>
+        <v>745686</v>
       </c>
       <c r="R42" t="n">
-        <v>7201169</v>
+        <v>7200954</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5468,16 +5468,16 @@
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530560</t>
+          <t>https://artportalen.se/Sighting/135530626</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135530598</v>
+        <v>135530578</v>
       </c>
       <c r="B43" t="n">
-        <v>80575</v>
+        <v>78863</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5485,21 +5485,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>745329</v>
+        <v>745042</v>
       </c>
       <c r="R43" t="n">
-        <v>7200885</v>
+        <v>7201067</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5584,16 +5584,16 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530598</t>
+          <t>https://artportalen.se/Sighting/135530578</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135530608</v>
+        <v>135530560</v>
       </c>
       <c r="B44" t="n">
-        <v>80575</v>
+        <v>79217</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,21 +5601,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5625,10 +5625,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>745270</v>
+        <v>745246</v>
       </c>
       <c r="R44" t="n">
-        <v>7200986</v>
+        <v>7201169</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5700,13 +5700,13 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530608</t>
+          <t>https://artportalen.se/Sighting/135530560</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135530613</v>
+        <v>135530598</v>
       </c>
       <c r="B45" t="n">
         <v>80575</v>
@@ -5741,10 +5741,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>745318</v>
+        <v>745329</v>
       </c>
       <c r="R45" t="n">
-        <v>7201025</v>
+        <v>7200885</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5786,12 +5786,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:08</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Bild</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5821,38 +5816,38 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530613</t>
+          <t>https://artportalen.se/Sighting/135530598</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135530599</v>
+        <v>135530608</v>
       </c>
       <c r="B46" t="n">
-        <v>80580</v>
+        <v>80575</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5862,10 +5857,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>745333</v>
+        <v>745270</v>
       </c>
       <c r="R46" t="n">
-        <v>7200883</v>
+        <v>7200986</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5897,7 +5892,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5907,7 +5902,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5937,38 +5932,38 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530599</t>
+          <t>https://artportalen.se/Sighting/135530608</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135530600</v>
+        <v>135530613</v>
       </c>
       <c r="B47" t="n">
-        <v>80586</v>
+        <v>80575</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5978,10 +5973,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>745333</v>
+        <v>745318</v>
       </c>
       <c r="R47" t="n">
-        <v>7200883</v>
+        <v>7201025</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6013,7 +6008,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6023,7 +6018,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6053,16 +6053,16 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530600</t>
+          <t>https://artportalen.se/Sighting/135530613</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135530609</v>
+        <v>135530599</v>
       </c>
       <c r="B48" t="n">
-        <v>80586</v>
+        <v>80580</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6070,21 +6070,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6094,10 +6094,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>745276</v>
+        <v>745333</v>
       </c>
       <c r="R48" t="n">
-        <v>7200976</v>
+        <v>7200883</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6169,56 +6169,51 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530609</t>
+          <t>https://artportalen.se/Sighting/135530599</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135530562</v>
+        <v>135530600</v>
       </c>
       <c r="B49" t="n">
-        <v>57993</v>
+        <v>80586</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>745221</v>
+        <v>745333</v>
       </c>
       <c r="R49" t="n">
-        <v>7201177</v>
+        <v>7200883</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6250,7 +6245,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6260,12 +6255,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bikder</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6295,56 +6285,51 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530562</t>
+          <t>https://artportalen.se/Sighting/135530600</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135530563</v>
+        <v>135530609</v>
       </c>
       <c r="B50" t="n">
-        <v>57993</v>
+        <v>80586</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>745147</v>
+        <v>745276</v>
       </c>
       <c r="R50" t="n">
-        <v>7201197</v>
+        <v>7200976</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6376,7 +6361,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6386,12 +6371,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack bilder</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6421,13 +6401,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530563</t>
+          <t>https://artportalen.se/Sighting/135530609</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135530564</v>
+        <v>135530562</v>
       </c>
       <c r="B51" t="n">
         <v>57993</v>
@@ -6467,10 +6447,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>745132</v>
+        <v>745221</v>
       </c>
       <c r="R51" t="n">
-        <v>7201209</v>
+        <v>7201177</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6502,7 +6482,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6512,12 +6492,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Äldre ringhack bikder</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6547,13 +6527,13 @@
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530564</t>
+          <t>https://artportalen.se/Sighting/135530562</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135530565</v>
+        <v>135530563</v>
       </c>
       <c r="B52" t="n">
         <v>57993</v>
@@ -6584,7 +6564,7 @@
       <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6593,10 +6573,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>745109</v>
+        <v>745147</v>
       </c>
       <c r="R52" t="n">
-        <v>7201209</v>
+        <v>7201197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6628,7 +6608,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6638,12 +6618,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack bilder</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6673,13 +6653,13 @@
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530565</t>
+          <t>https://artportalen.se/Sighting/135530563</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135530566</v>
+        <v>135530564</v>
       </c>
       <c r="B53" t="n">
         <v>57993</v>
@@ -6719,10 +6699,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>745100</v>
+        <v>745132</v>
       </c>
       <c r="R53" t="n">
-        <v>7201200</v>
+        <v>7201209</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6754,7 +6734,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6764,7 +6744,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6799,13 +6779,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530566</t>
+          <t>https://artportalen.se/Sighting/135530564</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135530573</v>
+        <v>135530565</v>
       </c>
       <c r="B54" t="n">
         <v>57993</v>
@@ -6845,10 +6825,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>745046</v>
+        <v>745109</v>
       </c>
       <c r="R54" t="n">
-        <v>7201117</v>
+        <v>7201209</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6880,7 +6860,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6890,12 +6870,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack bilder</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6925,13 +6905,13 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530573</t>
+          <t>https://artportalen.se/Sighting/135530565</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135530588</v>
+        <v>135530566</v>
       </c>
       <c r="B55" t="n">
         <v>57993</v>
@@ -6960,24 +6940,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>745362</v>
+        <v>745100</v>
       </c>
       <c r="R55" t="n">
-        <v>7200804</v>
+        <v>7201200</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7009,7 +6986,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7019,12 +6996,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7054,13 +7031,13 @@
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530588</t>
+          <t>https://artportalen.se/Sighting/135530566</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135530590</v>
+        <v>135530573</v>
       </c>
       <c r="B56" t="n">
         <v>57993</v>
@@ -7091,7 +7068,7 @@
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7100,10 +7077,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>745376</v>
+        <v>745046</v>
       </c>
       <c r="R56" t="n">
-        <v>7200807</v>
+        <v>7201117</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7135,7 +7112,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7145,12 +7122,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Äldre ringhack bild</t>
+          <t>Färska ringhack bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7180,13 +7157,13 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530590</t>
+          <t>https://artportalen.se/Sighting/135530573</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135530605</v>
+        <v>135530588</v>
       </c>
       <c r="B57" t="n">
         <v>57993</v>
@@ -7219,7 +7196,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7229,10 +7206,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>745287</v>
+        <v>745362</v>
       </c>
       <c r="R57" t="n">
-        <v>7200930</v>
+        <v>7200804</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7264,7 +7241,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7274,19 +7251,19 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Skalad gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="b">
         <v>0</v>
@@ -7309,13 +7286,13 @@
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530605</t>
+          <t>https://artportalen.se/Sighting/135530588</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135530610</v>
+        <v>135530590</v>
       </c>
       <c r="B58" t="n">
         <v>57993</v>
@@ -7344,24 +7321,21 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>745278</v>
+        <v>745376</v>
       </c>
       <c r="R58" t="n">
-        <v>7201005</v>
+        <v>7200807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7393,7 +7367,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7403,12 +7377,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska (?) ringhack</t>
+          <t>Äldre ringhack bild</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7438,13 +7412,13 @@
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530610</t>
+          <t>https://artportalen.se/Sighting/135530590</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135530612</v>
+        <v>135530605</v>
       </c>
       <c r="B59" t="n">
         <v>57993</v>
@@ -7473,21 +7447,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>745307</v>
+        <v>745287</v>
       </c>
       <c r="R59" t="n">
-        <v>7201037</v>
+        <v>7200930</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7519,7 +7496,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7529,19 +7506,19 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Skalad gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG59" t="b">
         <v>0</v>
@@ -7564,13 +7541,13 @@
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530612</t>
+          <t>https://artportalen.se/Sighting/135530605</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135530614</v>
+        <v>135530610</v>
       </c>
       <c r="B60" t="n">
         <v>57993</v>
@@ -7599,21 +7576,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>745306</v>
+        <v>745278</v>
       </c>
       <c r="R60" t="n">
-        <v>7201046</v>
+        <v>7201005</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7645,7 +7625,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7655,12 +7635,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Färska ringhack bild</t>
+          <t>Färska (?) ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7690,13 +7670,13 @@
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530614</t>
+          <t>https://artportalen.se/Sighting/135530610</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135530615</v>
+        <v>135530612</v>
       </c>
       <c r="B61" t="n">
         <v>57993</v>
@@ -7736,10 +7716,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>745282</v>
+        <v>745307</v>
       </c>
       <c r="R61" t="n">
-        <v>7201100</v>
+        <v>7201037</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7771,7 +7751,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7781,12 +7761,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Färska ringhack bild</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7816,13 +7796,13 @@
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530615</t>
+          <t>https://artportalen.se/Sighting/135530612</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135530619</v>
+        <v>135530614</v>
       </c>
       <c r="B62" t="n">
         <v>57993</v>
@@ -7853,7 +7833,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7862,10 +7842,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>745225</v>
+        <v>745306</v>
       </c>
       <c r="R62" t="n">
-        <v>7201291</v>
+        <v>7201046</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7897,7 +7877,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7907,12 +7887,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7942,16 +7922,16 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530619</t>
+          <t>https://artportalen.se/Sighting/135530614</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135530575</v>
+        <v>135530615</v>
       </c>
       <c r="B63" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7959,27 +7939,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7988,10 +7968,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>745036</v>
+        <v>745282</v>
       </c>
       <c r="R63" t="n">
-        <v>7201097</v>
+        <v>7201100</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8023,7 +8003,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8033,12 +8013,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Färska ringhack bild</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8068,16 +8048,16 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530575</t>
+          <t>https://artportalen.se/Sighting/135530615</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135530581</v>
+        <v>135530619</v>
       </c>
       <c r="B64" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8085,27 +8065,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8114,10 +8094,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>745092</v>
+        <v>745225</v>
       </c>
       <c r="R64" t="n">
-        <v>7200970</v>
+        <v>7201291</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8149,7 +8129,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8159,12 +8139,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Läte</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8194,13 +8174,13 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530581</t>
+          <t>https://artportalen.se/Sighting/135530619</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135530593</v>
+        <v>135530575</v>
       </c>
       <c r="B65" t="n">
         <v>58154</v>
@@ -8240,10 +8220,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>745345</v>
+        <v>745036</v>
       </c>
       <c r="R65" t="n">
-        <v>7200823</v>
+        <v>7201097</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8275,7 +8255,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8285,12 +8265,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Läten flera st</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8320,13 +8300,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530593</t>
+          <t>https://artportalen.se/Sighting/135530575</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135530595</v>
+        <v>135530581</v>
       </c>
       <c r="B66" t="n">
         <v>58154</v>
@@ -8366,10 +8346,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>745322</v>
+        <v>745092</v>
       </c>
       <c r="R66" t="n">
-        <v>7200832</v>
+        <v>7200970</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8401,7 +8381,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8411,12 +8391,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Läten</t>
+          <t>Läte</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8446,51 +8426,56 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530595</t>
+          <t>https://artportalen.se/Sighting/135530581</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135530624</v>
+        <v>135530593</v>
       </c>
       <c r="B67" t="n">
-        <v>98196</v>
+        <v>58154</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>745746</v>
+        <v>745345</v>
       </c>
       <c r="R67" t="n">
-        <v>7200976</v>
+        <v>7200823</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8522,7 +8507,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8532,7 +8517,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Läten flera st</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8562,51 +8552,56 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530624</t>
+          <t>https://artportalen.se/Sighting/135530593</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135530625</v>
+        <v>135530595</v>
       </c>
       <c r="B68" t="n">
-        <v>98196</v>
+        <v>58154</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>745727</v>
+        <v>745322</v>
       </c>
       <c r="R68" t="n">
-        <v>7200965</v>
+        <v>7200832</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8638,7 +8633,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8648,7 +8643,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Läten</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8678,16 +8678,16 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530625</t>
+          <t>https://artportalen.se/Sighting/135530595</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136735429</v>
+        <v>135530624</v>
       </c>
       <c r="B69" t="n">
-        <v>98219</v>
+        <v>98196</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8715,17 +8715,17 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Båtforsheden södra, Vb</t>
+          <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>745701</v>
+        <v>745746</v>
       </c>
       <c r="R69" t="n">
         <v>7200976</v>
       </c>
       <c r="S69" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8749,22 +8749,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8779,69 +8779,66 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>Boreala Svampskogar</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735429</t>
+          <t>https://artportalen.se/Sighting/135530624</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136827662</v>
+        <v>135530625</v>
       </c>
       <c r="B70" t="n">
-        <v>93440</v>
+        <v>98196</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>232140</v>
+        <v>221941</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Båtforsheden, Vb</t>
+          <t>Finnboberget, Vb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>745702</v>
+        <v>745727</v>
       </c>
       <c r="R70" t="n">
-        <v>7201121</v>
+        <v>7200965</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8868,22 +8865,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8898,53 +8895,53 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Petra Wikström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>Boreala Svampskogar</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136827662</t>
+          <t>https://artportalen.se/Sighting/135530625</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136735434</v>
+        <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>91585</v>
+        <v>98219</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>256703</v>
+        <v>221941</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8954,13 +8951,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>745585</v>
+        <v>745701</v>
       </c>
       <c r="R71" t="n">
-        <v>7201188</v>
+        <v>7200976</v>
       </c>
       <c r="S71" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8989,7 +8986,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8999,7 +8996,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9029,51 +9026,54 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136735434</t>
+          <t>https://artportalen.se/Sighting/136735429</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135530568</v>
+        <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>79483</v>
+        <v>93442</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>260591</v>
+        <v>232140</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Finnboberget, Vb</t>
+          <t>Båtforsheden, Vb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>745105</v>
+        <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201186</v>
+        <v>7201121</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9100,22 +9100,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9130,53 +9130,53 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Petra Wikström, Moa Björnberg Dillner, Moa Turid Lövdahl, Pia Edfors</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+          <t>Boreala Svampskogar</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135530568</t>
+          <t>https://artportalen.se/Sighting/136827662</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136735428</v>
+        <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>90784</v>
+        <v>91585</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6331677</v>
+        <v>256703</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spökfransskivling</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ripartites borealis</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>T.Ulvinen &amp; al.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9186,13 +9186,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>745701</v>
+        <v>745585</v>
       </c>
       <c r="R73" t="n">
-        <v>7200979</v>
+        <v>7201188</v>
       </c>
       <c r="S73" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9260,6 +9260,238 @@
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136735434</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135530568</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Finnboberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>745105</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7201186</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135530568</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136735428</v>
+      </c>
+      <c r="B75" t="n">
+        <v>90784</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6331677</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Spökfransskivling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Ripartites borealis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>T.Ulvinen &amp; al.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Båtforsheden södra, Vb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>745701</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7200979</v>
+      </c>
+      <c r="S75" t="n">
+        <v>24</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>Boreala Svampskogar</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136735428</t>
         </is>
@@ -9339,6 +9571,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91585</v>
+        <v>91587</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90784</v>
+        <v>90786</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201121</v>
+        <v>7201120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201121</v>
+        <v>7201120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91587</v>
+        <v>91589</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90786</v>
+        <v>90788</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91589</v>
+        <v>91591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90788</v>
+        <v>90790</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93059</v>
+        <v>93060</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93446</v>
+        <v>93447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91591</v>
+        <v>91592</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90790</v>
+        <v>90791</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91592</v>
+        <v>91598</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90791</v>
+        <v>90797</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Gillis Aronsson, Alexander Singer, Martin Axegård</t>
+          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87514</v>
+        <v>87518</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201121</v>
+        <v>7201120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93066</v>
+        <v>93070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201121</v>
+        <v>7201120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90797</v>
+        <v>90801</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner, Martin Axegård, Alexander Singer, Gillis Aronsson, Petra Wikström, Helena Björnström</t>
+          <t>Moa Björnberg Dillner, Helena Björnström, Petra Wikström, Alexander Singer, Martin Axegård</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87518</v>
+        <v>87520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93070</v>
+        <v>93072</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91602</v>
+        <v>91604</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90801</v>
+        <v>90803</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87520</v>
+        <v>87533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93072</v>
+        <v>93085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91604</v>
+        <v>91617</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90803</v>
+        <v>90816</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87533</v>
+        <v>87535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201121</v>
+        <v>7201120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201121</v>
+        <v>7201120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90816</v>
+        <v>90818</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87535</v>
+        <v>87538</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93087</v>
+        <v>93090</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91619</v>
+        <v>91622</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90818</v>
+        <v>90821</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87538</v>
+        <v>87548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93090</v>
+        <v>93100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91622</v>
+        <v>91632</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90821</v>
+        <v>90831</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87548</v>
+        <v>87549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>136735432</v>
       </c>
       <c r="B3" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>136735435</v>
       </c>
       <c r="B6" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         <v>136735430</v>
       </c>
       <c r="B8" t="n">
-        <v>93100</v>
+        <v>93101</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>136735426</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>136735427</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>136735433</v>
       </c>
       <c r="B12" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>136735429</v>
       </c>
       <c r="B71" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>136735434</v>
       </c>
       <c r="B73" t="n">
-        <v>91632</v>
+        <v>91633</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>136735428</v>
       </c>
       <c r="B75" t="n">
-        <v>90831</v>
+        <v>90832</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87549</v>
+        <v>87552</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201121</v>
+        <v>7201120</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201121</v>
+        <v>7201120</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136827667</v>
       </c>
       <c r="B2" t="n">
-        <v>87552</v>
+        <v>87557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>136827664</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>136827663</v>
       </c>
       <c r="B7" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>745702</v>
       </c>
       <c r="R7" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>745702</v>
       </c>
       <c r="R72" t="n">
-        <v>7201120</v>
+        <v>7201121</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 28631-2026 artfynd.xlsx
+++ b/artfynd/A 28631-2026 artfynd.xlsx
@@ -918,7 +918,7 @@
         <v>136835604</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93475</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>136835603</v>
       </c>
       <c r="B9" t="n">
-        <v>93453</v>
+        <v>93465</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136827662</v>
       </c>
       <c r="B72" t="n">
-        <v>93500</v>
+        <v>93512</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
